--- a/R_Training_Swetha_20260105/R_Walk_Through_Notes_Day53_ranking_func.xlsx
+++ b/R_Training_Swetha_20260105/R_Walk_Through_Notes_Day53_ranking_func.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="5">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="13">
   <si>
     <t>row_number()</t>
   </si>
@@ -39,19 +39,57 @@
   </si>
   <si>
     <t>arr_delay</t>
+  </si>
+  <si>
+    <t>LBORES</t>
+  </si>
+  <si>
+    <t>LBTESTCD</t>
+  </si>
+  <si>
+    <t>ALT</t>
+  </si>
+  <si>
+    <t>SUBJID</t>
+  </si>
+  <si>
+    <t>top4</t>
+  </si>
+  <si>
+    <t>Grades</t>
+  </si>
+  <si>
+    <t>Relative position</t>
+  </si>
+  <si>
+    <t>scale prespective</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Lucida Console"/>
+      <family val="3"/>
     </font>
   </fonts>
   <fills count="3">
@@ -80,9 +118,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -104,16 +146,16 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>11</xdr:col>
-      <xdr:colOff>304800</xdr:colOff>
-      <xdr:row>14</xdr:row>
-      <xdr:rowOff>57150</xdr:rowOff>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>437321</xdr:colOff>
+      <xdr:row>9</xdr:row>
+      <xdr:rowOff>106847</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>17</xdr:col>
-      <xdr:colOff>200562</xdr:colOff>
-      <xdr:row>18</xdr:row>
-      <xdr:rowOff>171572</xdr:rowOff>
+      <xdr:col>20</xdr:col>
+      <xdr:colOff>10062</xdr:colOff>
+      <xdr:row>14</xdr:row>
+      <xdr:rowOff>30769</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -130,8 +172,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="7724775" y="2724150"/>
-          <a:ext cx="3848637" cy="876422"/>
+          <a:off x="9399104" y="1821347"/>
+          <a:ext cx="3863132" cy="876422"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -406,7 +448,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="H6:L30"/>
+  <dimension ref="B6:O31"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="9" max="9" width="14" bestFit="1" customWidth="1"/>
@@ -415,7 +457,7 @@
     <col min="12" max="12" width="13.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="6" spans="8:12" x14ac:dyDescent="0.25">
+    <row r="6" spans="8:15" x14ac:dyDescent="0.25">
       <c r="I6" t="s">
         <v>0</v>
       </c>
@@ -429,7 +471,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="7" spans="8:12" x14ac:dyDescent="0.25">
+    <row r="7" spans="8:15" x14ac:dyDescent="0.25">
       <c r="H7">
         <v>10</v>
       </c>
@@ -447,7 +489,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="8:12" x14ac:dyDescent="0.25">
+    <row r="8" spans="8:15" x14ac:dyDescent="0.25">
       <c r="H8" s="1">
         <v>20</v>
       </c>
@@ -464,8 +506,14 @@
         <f t="shared" ref="L8:L10" si="0">(J8-1)/(4-1)</f>
         <v>0.33333333333333331</v>
       </c>
-    </row>
-    <row r="9" spans="8:12" x14ac:dyDescent="0.25">
+      <c r="N8" t="s">
+        <v>11</v>
+      </c>
+      <c r="O8" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="9" spans="8:15" x14ac:dyDescent="0.25">
       <c r="H9" s="1">
         <v>20</v>
       </c>
@@ -483,7 +531,7 @@
         <v>0.33333333333333331</v>
       </c>
     </row>
-    <row r="10" spans="8:12" x14ac:dyDescent="0.25">
+    <row r="10" spans="8:15" x14ac:dyDescent="0.25">
       <c r="H10">
         <v>40</v>
       </c>
@@ -501,7 +549,119 @@
         <v>1</v>
       </c>
     </row>
-    <row r="25" spans="9:12" x14ac:dyDescent="0.25">
+    <row r="11" spans="8:15" x14ac:dyDescent="0.25">
+      <c r="J11" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="8:15" x14ac:dyDescent="0.25">
+      <c r="H12" s="3">
+        <v>851</v>
+      </c>
+      <c r="J12">
+        <v>1</v>
+      </c>
+      <c r="L12">
+        <f>(J12-1)/(7-1)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="8:15" x14ac:dyDescent="0.25">
+      <c r="H13" s="3">
+        <v>456</v>
+      </c>
+      <c r="J13">
+        <v>2</v>
+      </c>
+      <c r="L13">
+        <f t="shared" ref="L13:L18" si="1">(J13-1)/(7-1)</f>
+        <v>0.16666666666666666</v>
+      </c>
+    </row>
+    <row r="14" spans="8:15" x14ac:dyDescent="0.25">
+      <c r="H14" s="3">
+        <v>456</v>
+      </c>
+      <c r="J14">
+        <v>2</v>
+      </c>
+      <c r="L14">
+        <f t="shared" si="1"/>
+        <v>0.16666666666666666</v>
+      </c>
+    </row>
+    <row r="15" spans="8:15" x14ac:dyDescent="0.25">
+      <c r="H15" s="3">
+        <v>359</v>
+      </c>
+      <c r="J15">
+        <v>4</v>
+      </c>
+      <c r="L15">
+        <f t="shared" si="1"/>
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="16" spans="8:15" x14ac:dyDescent="0.25">
+      <c r="H16" s="3">
+        <v>270</v>
+      </c>
+      <c r="J16">
+        <v>5</v>
+      </c>
+      <c r="L16">
+        <f t="shared" si="1"/>
+        <v>0.66666666666666663</v>
+      </c>
+    </row>
+    <row r="17" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="H17" s="3">
+        <v>270</v>
+      </c>
+      <c r="J17">
+        <v>5</v>
+      </c>
+      <c r="L17">
+        <f t="shared" si="1"/>
+        <v>0.66666666666666663</v>
+      </c>
+    </row>
+    <row r="18" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="H18" s="3">
+        <v>172</v>
+      </c>
+      <c r="J18">
+        <v>7</v>
+      </c>
+      <c r="L18">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="24" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="E24" t="s">
+        <v>9</v>
+      </c>
+      <c r="F24" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="25" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B25" t="s">
+        <v>8</v>
+      </c>
+      <c r="C25" t="s">
+        <v>6</v>
+      </c>
+      <c r="D25" t="s">
+        <v>5</v>
+      </c>
+      <c r="E25" t="s">
+        <v>1</v>
+      </c>
+      <c r="F25" t="s">
+        <v>2</v>
+      </c>
       <c r="I25" t="s">
         <v>4</v>
       </c>
@@ -515,7 +675,19 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="9:12" x14ac:dyDescent="0.25">
+    <row r="26" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="C26" t="s">
+        <v>7</v>
+      </c>
+      <c r="D26">
+        <v>43.2</v>
+      </c>
+      <c r="E26">
+        <v>1</v>
+      </c>
+      <c r="F26">
+        <v>1</v>
+      </c>
       <c r="I26">
         <v>100</v>
       </c>
@@ -529,7 +701,19 @@
         <v>1</v>
       </c>
     </row>
-    <row r="27" spans="9:12" x14ac:dyDescent="0.25">
+    <row r="27" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="C27" t="s">
+        <v>7</v>
+      </c>
+      <c r="D27">
+        <v>43.2</v>
+      </c>
+      <c r="E27">
+        <v>1</v>
+      </c>
+      <c r="F27">
+        <v>1</v>
+      </c>
       <c r="I27">
         <v>90</v>
       </c>
@@ -543,7 +727,19 @@
         <v>2</v>
       </c>
     </row>
-    <row r="28" spans="9:12" x14ac:dyDescent="0.25">
+    <row r="28" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="C28" t="s">
+        <v>7</v>
+      </c>
+      <c r="D28" s="2">
+        <v>43.6</v>
+      </c>
+      <c r="E28">
+        <v>3</v>
+      </c>
+      <c r="F28">
+        <v>2</v>
+      </c>
       <c r="I28">
         <v>90</v>
       </c>
@@ -557,7 +753,19 @@
         <v>3</v>
       </c>
     </row>
-    <row r="29" spans="9:12" x14ac:dyDescent="0.25">
+    <row r="29" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="C29" t="s">
+        <v>7</v>
+      </c>
+      <c r="D29" s="2">
+        <v>43.7</v>
+      </c>
+      <c r="E29">
+        <v>4</v>
+      </c>
+      <c r="F29">
+        <v>3</v>
+      </c>
       <c r="I29">
         <v>80</v>
       </c>
@@ -571,7 +779,19 @@
         <v>4</v>
       </c>
     </row>
-    <row r="30" spans="9:12" x14ac:dyDescent="0.25">
+    <row r="30" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="C30" t="s">
+        <v>7</v>
+      </c>
+      <c r="D30" s="2">
+        <v>43.8</v>
+      </c>
+      <c r="E30">
+        <v>5</v>
+      </c>
+      <c r="F30">
+        <v>4</v>
+      </c>
       <c r="I30">
         <v>70</v>
       </c>
@@ -585,8 +805,23 @@
         <v>5</v>
       </c>
     </row>
+    <row r="31" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="C31" t="s">
+        <v>7</v>
+      </c>
+      <c r="D31">
+        <v>44.3</v>
+      </c>
+      <c r="E31">
+        <v>6</v>
+      </c>
+      <c r="F31">
+        <v>5</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <drawing r:id="rId1"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <drawing r:id="rId2"/>
 </worksheet>
 </file>